--- a/Mechanical system part list_CN.xlsx
+++ b/Mechanical system part list_CN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\showcase\手搓智驾1_底盘\2.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\showcase\手搓智驾1_底盘\Aluminum-profile-go-kart-v2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD05D71-87F3-4D25-A8D3-EFB444539463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6101508B-826E-46E0-AEA8-4A03100F5631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$K$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$K$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="83">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -378,10 +378,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>悬架，前轮，转向总成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://item.taobao.com/item.htm?app=weixin&amp;bc_fl_src=share-1041336559083290-2-1&amp;bxsign=scdtfgvWwkqcjUDpXw5p-jKbndyOVl5LQK7D-U2ELLhhGWk9YnFmW0mn-R2D8cW9PCmSer2j1Q0epj0rx0hcwMtysBrj1xk8j8akbRLFHFjr6nojdFfs6GXU-abjIZTwD-7ykRDPmPnYTNRrcr7RzKbKQ&amp;cpp=1&amp;h5_spm=a-tb-item.b-tb-item&amp;id=1013688821175&amp;share_crt_v=1&amp;shareurl=true&amp;short_name=h.7lxKJJentOcXikj&amp;sp_tk=amlxYlUzdEZtMEU%3D&amp;spm=a2159r.13376460.0.0&amp;tbSocialPopKey=shareItem&amp;tk=jiqbU3tFm0E&amp;un=8791517a4fc147ba398cb0a405e958bd&amp;un_site=0&amp;ut_sk=1.aDxKqD%2FLA28DAO8nje8YZMRD_21646297_1768466248573.TaoPassword-WeiXin.1&amp;wxsign=tbwvDX7R3dtUjK9amo3L7HOkw4kvwvP4BEGR_PqA8q7a3xFG4ypZsp8HaZ3dOPrOpHr3_PmmQZb5dfANQlxIx4vo2q3A3-PiGTE06F0KpFdP8YSZ-MZthEi0WUF4ispTOxxReUb5Bo1jJ8Ryobx-J_71Q&amp;x-ssr=true</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -424,6 +420,18 @@
   </si>
   <si>
     <t>长度400mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>转向总成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?app=chrome&amp;bxsign=scdQCwgjnOrASI_zpd7PNMWcXMkePw5gDpky8idcRzoxCYicTvBpWMQgY4MAKLftkv_GDlUMo2o4dBe5mUS1mjPl0EHfllKM_2LiREWUKXDBHVliW7gvW1SRx6QWOuWcsPVTFwggfbX2KgEvfG902hfzA&amp;cpp=1&amp;id=1041199945900&amp;price=349&amp;shareUniqueId=35616769085&amp;share_crt_v=1&amp;shareurl=true&amp;short_name=h.iOIM4S5ZtF7UzOA&amp;skuId=6225421574987&amp;sourceType=item&amp;sp_tk=ZjBsTDVld0FqYlc%3D&amp;spm=a2159r.13376460.0.0&amp;suid=37ccf6df-6cf5-4def-94d5-82672d7108f2&amp;tbSocialPopKey=shareItem&amp;tk=f0lL5ewAjbW&amp;un=8791517a4fc147ba398cb0a405e958bd&amp;un_site=0&amp;ut_sk=1.aDxKqD%2FLA28DAO8nje8YZMRD_21646297_1775523333697.Copy.1&amp;wxsign=tbw-p1Yvf7KHoFI_HmPPCj65-JbOitxluOU0MVMAX2jrxYMX9n4tOTNlTRmGBAJZn0U0GJtir8fD28nhv__ldfrgKdYkcKmY09g0u2cKy9sXvBZ3FK-qYBT07MvvKH3E4H_jkWl2rRLZBxPDQ6MwdOx9w</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>悬架，前轮</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -667,7 +675,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -729,6 +737,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -780,8 +794,8 @@
     <xf numFmtId="14" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1026,58 +1040,14 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>456248</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>208849</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>2987993</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>2836138</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="图片 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF2BF386-622A-3674-5DDC-BCE8831B23DC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15779592" y="13901037"/>
-          <a:ext cx="2520315" cy="2631099"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
       <xdr:colOff>561027</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>287655</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>1981501</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>1696236</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1094,7 +1064,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1103,6 +1073,94 @@
         <a:xfrm>
           <a:off x="15884371" y="20409218"/>
           <a:ext cx="1420474" cy="1400961"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>702468</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>145723</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1762125</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>1570452</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="图片 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40292AB2-2B72-41A8-8175-B01F2DCAD186}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17742693" y="13804573"/>
+          <a:ext cx="1059657" cy="1424729"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>488157</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>881062</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>2559845</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>2468217</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="图片 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6E4FF46-E559-4A50-9B39-EC71D473956F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17537907" y="16121062"/>
+          <a:ext cx="2071688" cy="1587155"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1380,77 +1438,77 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:L30"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:L31"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" customWidth="1"/>
-    <col min="3" max="3" width="25.44140625" customWidth="1"/>
+    <col min="1" max="1" width="16.625" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="25.5" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="37.109375" customWidth="1"/>
-    <col min="6" max="6" width="28.77734375" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" customWidth="1"/>
-    <col min="9" max="9" width="56.88671875" customWidth="1"/>
-    <col min="10" max="10" width="44.44140625" customWidth="1"/>
-    <col min="11" max="12" width="33.44140625" customWidth="1"/>
+    <col min="5" max="5" width="37.125" customWidth="1"/>
+    <col min="6" max="6" width="28.75" customWidth="1"/>
+    <col min="8" max="8" width="8.875" customWidth="1"/>
+    <col min="9" max="9" width="56.875" customWidth="1"/>
+    <col min="10" max="10" width="44.5" customWidth="1"/>
+    <col min="11" max="12" width="33.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="46.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+    <row r="2" spans="1:12" ht="46.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
       <c r="L2" s="15"/>
     </row>
-    <row r="3" spans="1:12" s="2" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+    <row r="3" spans="1:12" s="2" customFormat="1" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="37">
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="39">
         <v>46037</v>
       </c>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="36" t="s">
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="36"/>
-      <c r="J3" s="32" t="s">
+      <c r="I3" s="38"/>
+      <c r="J3" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="33"/>
-    </row>
-    <row r="4" spans="1:12" ht="160.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="K3" s="35"/>
+    </row>
+    <row r="4" spans="1:12" ht="160.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="34" t="s">
+      <c r="B4" s="26"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
       <c r="L4" s="16"/>
     </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" s="1" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>0</v>
       </c>
@@ -1486,9 +1544,9 @@
       </c>
       <c r="L5" s="17"/>
     </row>
-    <row r="6" spans="1:12" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B6" s="4"/>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="28" t="s">
         <v>42</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -1510,17 +1568,17 @@
         <v>62</v>
       </c>
       <c r="J6" s="4"/>
-      <c r="K6" s="29" t="s">
+      <c r="K6" s="31" t="s">
         <v>57</v>
       </c>
       <c r="L6" s="12"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>1</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="27"/>
+      <c r="C7" s="29"/>
       <c r="D7" s="4" t="s">
         <v>10</v>
       </c>
@@ -1536,15 +1594,15 @@
       <c r="H7" s="4"/>
       <c r="I7" s="5"/>
       <c r="J7" s="4"/>
-      <c r="K7" s="30"/>
+      <c r="K7" s="32"/>
       <c r="L7" s="12"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>2</v>
       </c>
       <c r="B8" s="4"/>
-      <c r="C8" s="27"/>
+      <c r="C8" s="29"/>
       <c r="D8" s="4" t="s">
         <v>18</v>
       </c>
@@ -1560,23 +1618,23 @@
       <c r="H8" s="4"/>
       <c r="I8" s="5"/>
       <c r="J8" s="4"/>
-      <c r="K8" s="30"/>
+      <c r="K8" s="32"/>
       <c r="L8" s="12"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>3</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="27"/>
+      <c r="C9" s="29"/>
       <c r="D9" s="4" t="s">
         <v>25</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="38" t="s">
-        <v>80</v>
+      <c r="F9" s="22" t="s">
+        <v>79</v>
       </c>
       <c r="G9" s="4">
         <v>2</v>
@@ -1586,15 +1644,15 @@
         <v>60</v>
       </c>
       <c r="J9" s="4"/>
-      <c r="K9" s="30"/>
+      <c r="K9" s="32"/>
       <c r="L9" s="12"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>4</v>
       </c>
       <c r="B10" s="4"/>
-      <c r="C10" s="27"/>
+      <c r="C10" s="29"/>
       <c r="D10" s="4" t="s">
         <v>23</v>
       </c>
@@ -1610,15 +1668,15 @@
       <c r="H10" s="4"/>
       <c r="I10" s="5"/>
       <c r="J10" s="4"/>
-      <c r="K10" s="30"/>
+      <c r="K10" s="32"/>
       <c r="L10" s="12"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>5</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="27"/>
+      <c r="C11" s="29"/>
       <c r="D11" s="4" t="s">
         <v>19</v>
       </c>
@@ -1634,15 +1692,15 @@
       <c r="H11" s="4"/>
       <c r="I11" s="5"/>
       <c r="J11" s="4"/>
-      <c r="K11" s="30"/>
+      <c r="K11" s="32"/>
       <c r="L11" s="12"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>6</v>
       </c>
       <c r="B12" s="4"/>
-      <c r="C12" s="27"/>
+      <c r="C12" s="29"/>
       <c r="D12" s="4" t="s">
         <v>20</v>
       </c>
@@ -1658,15 +1716,15 @@
       <c r="H12" s="4"/>
       <c r="I12" s="5"/>
       <c r="J12" s="4"/>
-      <c r="K12" s="30"/>
+      <c r="K12" s="32"/>
       <c r="L12" s="12"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>7</v>
       </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="27"/>
+      <c r="C13" s="29"/>
       <c r="D13" s="4" t="s">
         <v>22</v>
       </c>
@@ -1682,15 +1740,15 @@
       <c r="H13" s="4"/>
       <c r="I13" s="5"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="30"/>
+      <c r="K13" s="32"/>
       <c r="L13" s="12"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>8</v>
       </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="27"/>
+      <c r="C14" s="29"/>
       <c r="D14" s="4" t="s">
         <v>24</v>
       </c>
@@ -1706,15 +1764,15 @@
       <c r="H14" s="4"/>
       <c r="I14" s="5"/>
       <c r="J14" s="4"/>
-      <c r="K14" s="30"/>
+      <c r="K14" s="32"/>
       <c r="L14" s="12"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>9</v>
       </c>
       <c r="B15" s="4"/>
-      <c r="C15" s="27"/>
+      <c r="C15" s="29"/>
       <c r="D15" s="4" t="s">
         <v>27</v>
       </c>
@@ -1730,15 +1788,15 @@
       <c r="H15" s="4"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
-      <c r="K15" s="30"/>
+      <c r="K15" s="32"/>
       <c r="L15" s="12"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>10</v>
       </c>
       <c r="B16" s="4"/>
-      <c r="C16" s="27"/>
+      <c r="C16" s="29"/>
       <c r="D16" s="4" t="s">
         <v>28</v>
       </c>
@@ -1754,15 +1812,15 @@
       <c r="H16" s="4"/>
       <c r="I16" s="5"/>
       <c r="J16" s="4"/>
-      <c r="K16" s="30"/>
+      <c r="K16" s="32"/>
       <c r="L16" s="12"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>11</v>
       </c>
       <c r="B17" s="4"/>
-      <c r="C17" s="27"/>
+      <c r="C17" s="29"/>
       <c r="D17" s="4" t="s">
         <v>33</v>
       </c>
@@ -1782,15 +1840,15 @@
         <v>68</v>
       </c>
       <c r="J17" s="4"/>
-      <c r="K17" s="30"/>
+      <c r="K17" s="32"/>
       <c r="L17" s="12"/>
     </row>
-    <row r="18" spans="1:12" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="130.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>12</v>
       </c>
       <c r="B18" s="4"/>
-      <c r="C18" s="27"/>
+      <c r="C18" s="29"/>
       <c r="D18" s="4" t="s">
         <v>35</v>
       </c>
@@ -1806,15 +1864,15 @@
       </c>
       <c r="I18" s="5"/>
       <c r="J18" s="4"/>
-      <c r="K18" s="30"/>
+      <c r="K18" s="32"/>
       <c r="L18" s="12"/>
     </row>
-    <row r="19" spans="1:12" ht="123.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="123.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>13</v>
       </c>
       <c r="B19" s="4"/>
-      <c r="C19" s="27"/>
+      <c r="C19" s="29"/>
       <c r="D19" s="4" t="s">
         <v>37</v>
       </c>
@@ -1830,15 +1888,15 @@
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="4"/>
-      <c r="K19" s="30"/>
+      <c r="K19" s="32"/>
       <c r="L19" s="12"/>
     </row>
-    <row r="20" spans="1:12" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>14</v>
       </c>
       <c r="B20" s="4"/>
-      <c r="C20" s="27"/>
+      <c r="C20" s="29"/>
       <c r="D20" s="4" t="s">
         <v>38</v>
       </c>
@@ -1854,15 +1912,15 @@
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="4"/>
-      <c r="K20" s="30"/>
+      <c r="K20" s="32"/>
       <c r="L20" s="12"/>
     </row>
-    <row r="21" spans="1:12" ht="121.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="121.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>15</v>
       </c>
       <c r="B21" s="4"/>
-      <c r="C21" s="27"/>
+      <c r="C21" s="29"/>
       <c r="D21" s="4" t="s">
         <v>39</v>
       </c>
@@ -1878,15 +1936,15 @@
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="4"/>
-      <c r="K21" s="30"/>
+      <c r="K21" s="32"/>
       <c r="L21" s="12"/>
     </row>
-    <row r="22" spans="1:12" ht="127.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="127.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>16</v>
       </c>
       <c r="B22" s="4"/>
-      <c r="C22" s="28"/>
+      <c r="C22" s="30"/>
       <c r="D22" s="4" t="s">
         <v>40</v>
       </c>
@@ -1902,131 +1960,125 @@
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="4"/>
-      <c r="K22" s="30"/>
+      <c r="K22" s="32"/>
       <c r="L22" s="12"/>
     </row>
-    <row r="23" spans="1:12" ht="251.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="127.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>17</v>
       </c>
       <c r="B23" s="4"/>
-      <c r="C23" s="4" t="s">
-        <v>69</v>
+      <c r="C23" s="21" t="s">
+        <v>80</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>43</v>
       </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
-      <c r="G23" s="4">
-        <v>1</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I23" s="8"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="5"/>
       <c r="J23" s="4"/>
-      <c r="K23" s="9" t="s">
-        <v>70</v>
+      <c r="K23" s="40" t="s">
+        <v>81</v>
       </c>
       <c r="L23" s="12"/>
     </row>
-    <row r="24" spans="1:12" ht="82.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="251.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>18</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>43</v>
       </c>
       <c r="E24" s="4"/>
-      <c r="F24" s="4" t="s">
-        <v>76</v>
-      </c>
+      <c r="F24" s="4"/>
       <c r="G24" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="I24" s="20" t="s">
-        <v>78</v>
-      </c>
+      <c r="I24" s="8"/>
       <c r="J24" s="4"/>
       <c r="K24" s="9" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L24" s="12"/>
     </row>
-    <row r="25" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="82.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>19</v>
       </c>
-      <c r="B25" s="7"/>
+      <c r="B25" s="4"/>
       <c r="C25" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>73</v>
+      <c r="D25" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="G25" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I25" s="5"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="L25" s="18"/>
-    </row>
-    <row r="26" spans="1:12" ht="156" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="I25" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="J25" s="4"/>
+      <c r="K25" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="L25" s="12"/>
+    </row>
+    <row r="26" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>20</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
+        <v>73</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="G26" s="4">
         <v>1</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I26" s="5" t="s">
-        <v>72</v>
-      </c>
+      <c r="I26" s="5"/>
       <c r="J26" s="7"/>
-      <c r="K26" s="19" t="s">
-        <v>71</v>
+      <c r="K26" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="L26" s="18"/>
     </row>
-    <row r="27" spans="1:12" ht="147.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="156" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>21</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="9" t="s">
-        <v>44</v>
+      <c r="B27" s="7"/>
+      <c r="C27" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -2034,81 +2086,109 @@
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J27" s="4"/>
-      <c r="K27" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="L27" s="12"/>
-    </row>
-    <row r="28" spans="1:12" ht="107.4" customHeight="1" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J27" s="7"/>
+      <c r="K27" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="L27" s="18"/>
+    </row>
+    <row r="28" spans="1:12" ht="147.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>22</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="4" t="s">
-        <v>45</v>
+      <c r="B28" s="4"/>
+      <c r="C28" s="9" t="s">
+        <v>44</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>46</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
       <c r="G28" s="4">
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="I28" s="10" t="s">
+      <c r="I28" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J28" s="4"/>
+      <c r="K28" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="L28" s="12"/>
+    </row>
+    <row r="29" spans="1:12" ht="107.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="4">
+        <v>23</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G29" s="4">
+        <v>1</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J28" s="7"/>
-      <c r="L28" s="18"/>
-    </row>
-    <row r="29" spans="1:12" ht="55.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+      <c r="J29" s="7"/>
+      <c r="L29" s="18"/>
+    </row>
+    <row r="30" spans="1:12" ht="55.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
-      <c r="L29" s="14"/>
-    </row>
-    <row r="30" spans="1:12" ht="55.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="12"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
+      <c r="B30" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="24"/>
+      <c r="K30" s="24"/>
       <c r="L30" s="14"/>
+    </row>
+    <row r="31" spans="1:12" ht="55.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="12"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B29:K29"/>
+    <mergeCell ref="B30:K30"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="C6:C22"/>
     <mergeCell ref="K6:K22"/>
@@ -2121,10 +2201,10 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="K26" r:id="rId1" display="https://item.taobao.com/item.htm?abbucket=19&amp;id=885032361201&amp;mi_id=0000jfJCKwilSELr-zj6p1uyrAQwxlg-lD2tJdTGwlUgR0Q&amp;ns=1&amp;priceTId=214784af17684674532951853e134d&amp;skuId=5893464791989&amp;spm=a21n57.1.hoverItem.2&amp;utparam=%7B%22aplus_abtest%22%3A%2225b53b868684608ed1ab462bacf635cd%22%7D&amp;xxc=taobaoSearch" xr:uid="{8F128C67-311B-47D8-AE93-CC2347C1CC97}"/>
+    <hyperlink ref="K27" r:id="rId1" display="https://item.taobao.com/item.htm?abbucket=19&amp;id=885032361201&amp;mi_id=0000jfJCKwilSELr-zj6p1uyrAQwxlg-lD2tJdTGwlUgR0Q&amp;ns=1&amp;priceTId=214784af17684674532951853e134d&amp;skuId=5893464791989&amp;spm=a21n57.1.hoverItem.2&amp;utparam=%7B%22aplus_abtest%22%3A%2225b53b868684608ed1ab462bacf635cd%22%7D&amp;xxc=taobaoSearch" xr:uid="{8F128C67-311B-47D8-AE93-CC2347C1CC97}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.44" top="0.25" bottom="0.16" header="0.12" footer="0.09"/>
-  <pageSetup paperSize="9" scale="30" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="29" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/Mechanical system part list_CN.xlsx
+++ b/Mechanical system part list_CN.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\showcase\手搓智驾1_底盘\Aluminum-profile-go-kart-v2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6101508B-826E-46E0-AEA8-4A03100F5631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E6D577-7C71-4732-97EB-AE788DD2E9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$K$30</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="90">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -378,10 +375,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>https://item.taobao.com/item.htm?app=weixin&amp;bc_fl_src=share-1041336559083290-2-1&amp;bxsign=scdtfgvWwkqcjUDpXw5p-jKbndyOVl5LQK7D-U2ELLhhGWk9YnFmW0mn-R2D8cW9PCmSer2j1Q0epj0rx0hcwMtysBrj1xk8j8akbRLFHFjr6nojdFfs6GXU-abjIZTwD-7ykRDPmPnYTNRrcr7RzKbKQ&amp;cpp=1&amp;h5_spm=a-tb-item.b-tb-item&amp;id=1013688821175&amp;share_crt_v=1&amp;shareurl=true&amp;short_name=h.7lxKJJentOcXikj&amp;sp_tk=amlxYlUzdEZtMEU%3D&amp;spm=a2159r.13376460.0.0&amp;tbSocialPopKey=shareItem&amp;tk=jiqbU3tFm0E&amp;un=8791517a4fc147ba398cb0a405e958bd&amp;un_site=0&amp;ut_sk=1.aDxKqD%2FLA28DAO8nje8YZMRD_21646297_1768466248573.TaoPassword-WeiXin.1&amp;wxsign=tbwvDX7R3dtUjK9amo3L7HOkw4kvwvP4BEGR_PqA8q7a3xFG4ypZsp8HaZ3dOPrOpHr3_PmmQZb5dfANQlxIx4vo2q3A3-PiGTE06F0KpFdP8YSZ-MZthEi0WUF4ispTOxxReUb5Bo1jJ8Ryobx-J_71Q&amp;x-ssr=true</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>https://item.taobao.com/item.htm?abbucket=19&amp;id=885032361201&amp;mi_id=0000jfJCKwilSELr-zj6p1uyrAQwxlg-lD2tJdTGwlUgR0Q&amp;ns=1&amp;priceTId=214784af17684674532951853e134d&amp;skuId=5893464791989&amp;spm=a21n57.1.hoverItem.2&amp;utparam=%7B%22aplus_abtest%22%3A%2225b53b868684608ed1ab462bacf635cd%22%7D&amp;xxc=taobaoSearch</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -432,6 +425,38 @@
   </si>
   <si>
     <t>悬架，前轮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?app=chrome&amp;bxsign=scdl_WkxoXxUqHjdQTxAqyGCeyNW6xqZGQJRXC8eUqwFx7XNnrKxPQfqmirng2ooozSNIBzwCSfnxVIVZeux9GFtNuOWup88HLF6fDWQXZbAz-Qu_6HoHCQg999NZaf43tk0x6Gu9dpTRmsQUM4nBxLpw&amp;cpp=1&amp;id=1042357996635&amp;price=499&amp;shareUniqueId=35627641537&amp;share_crt_v=1&amp;shareurl=true&amp;short_name=h.iNqLNkjWBtNC2sU&amp;sourceType=item&amp;sp_tk=Q1dhYjVWcjk5RGU%3D&amp;spm=a2159r.13376460.0.0&amp;suid=85a470ae-f4fb-4e41-8714-13625bcb3e1c&amp;tbSocialPopKey=shareItem&amp;tk=CWab5Vr99De%20MF937&amp;un=8791517a4fc147ba398cb0a405e958bd&amp;un_site=0&amp;ut_sk=1.aDxKqD%2FLA28DAO8nje8YZMRD_21646297_1775635333136.Copy.1&amp;wxsign=tbwQef1klLeb8GMY_PeH3bWL4SgwIdUIpihsjAy8-bj_kHd45FTlQRF2WfJrNVtiA9ueCa74hyoqGrCxZYs-lXjwRtCXgD9gnWpqbZWBUOoAwjicGqi7gvr5VFjtai-ZVAmm7ysj5P9e4UdXAKfVj8cSA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刹车踏板及刹车盒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可选，也可采用电路板自带的电机电刹，但效果不如机械刹车效果好，自行选择</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?app=chrome&amp;bxsign=scd7Qzz_qaf9uMOgSkXlG8L5CsWSogOwnoGGJJecIyjyUuN0hnbAfiwJick0IyK2RbVdsamxoGix4_YIOlT1UrH6wfI_KRJxwd_PCM82WHtQs-5xJjz2JRJvoPJAfZpuiCm7RQ_y1aGgps7zw_cE9_tdA&amp;cpp=1&amp;id=1042343392622&amp;price=169&amp;shareUniqueId=35627528719&amp;share_crt_v=1&amp;shareurl=true&amp;short_name=h.imNlnnjLgrccmj5&amp;sourceType=item&amp;sp_tk=cUZWMDVWck9WM1o%3D&amp;spm=a2159r.13376460.0.0&amp;suid=da73b970-a85b-45a7-b2e8-80b942b61046&amp;tbSocialPopKey=shareItem&amp;tk=qFV05VrOV3Z%20HU006&amp;un=8791517a4fc147ba398cb0a405e958bd&amp;un_site=0&amp;ut_sk=1.aDxKqD%2FLA28DAO8nje8YZMRD_21646297_1775635353919.Copy.1&amp;wxsign=tbwWJ6OvJWKSYj4OCg9DoYIIgiw1aX65mnlQL6GnySbntmlH8WQ7DPYs89xBvdaKv5jWD9sBgFcyZZ8IBCgHDpFtBeKk202jJ6d_3zRFdsh54n1oXgO-DHtD1Q8uP1VPyc-z7aY5oGG91gIXrg993H53A&amp;skuId=6225941162782</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刹车卡钳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安装孔距需要与羊角匹配，孔距51mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?from=cart&amp;id=991045469772&amp;mi_id=00003sRYgPiZd_8FNhAwnbN5mDeUhC6TDkPfsiqQabrvaT0&amp;skuId=5960300029207&amp;spm=a1z0d.6639537%2F202410.item.d991045469772.de1b74848rqgUQ&amp;upStreamPrice=900</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>左右各一只，同上配套，可选</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -439,7 +464,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -542,6 +567,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -675,7 +707,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -744,6 +776,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -794,9 +829,13 @@
     <xf numFmtId="14" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -820,50 +859,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>506730</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>154940</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>1541780</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>1502663</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="图片 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C26E34D-278F-4271-AE74-A48D7BF3AB8A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12419330" y="13121640"/>
-          <a:ext cx="1042670" cy="1338198"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
       <xdr:colOff>406400</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
@@ -871,8 +866,8 @@
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>1770380</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>1257406</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>106</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -888,7 +883,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -908,22 +903,66 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>546100</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>292100</xdr:rowOff>
+      <xdr:colOff>641667</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>71597</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1980059</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>1241072</xdr:rowOff>
+      <xdr:colOff>1381125</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1034434</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2">
+        <xdr:cNvPr id="6" name="图片 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FF2D91D-6C50-430E-8611-A3C17935BFFA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A77976D-4E4E-4839-BD89-7E1209EED900}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18196242" y="9853772"/>
+          <a:ext cx="739458" cy="962837"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>530225</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>117475</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1555750</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>796152</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="图片 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB6E9993-9308-4B94-ADD6-6192BAEB31B9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -939,8 +978,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12458700" y="8699500"/>
-          <a:ext cx="1433959" cy="941352"/>
+          <a:off x="18084800" y="7842250"/>
+          <a:ext cx="1025525" cy="678677"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -954,20 +993,20 @@
       <xdr:col>9</xdr:col>
       <xdr:colOff>546099</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>254000</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1850601</xdr:colOff>
+      <xdr:colOff>1428750</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>1485900</xdr:rowOff>
+      <xdr:rowOff>928777</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="图片 3">
+        <xdr:cNvPr id="13" name="图片 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C39A8DD-30D1-4BFD-8061-06E9C55F8449}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B45165E-9D8A-432C-B413-2A26CA6936EB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -983,8 +1022,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12458699" y="10185400"/>
-          <a:ext cx="1314027" cy="1231900"/>
+          <a:off x="18100674" y="8734425"/>
+          <a:ext cx="882651" cy="833527"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -996,22 +1035,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:colOff>228601</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>36119</xdr:rowOff>
+      <xdr:rowOff>36120</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>2114486</xdr:colOff>
+      <xdr:colOff>1333501</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>1333501</xdr:rowOff>
+      <xdr:rowOff>796228</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="图片 4">
+        <xdr:cNvPr id="14" name="图片 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C98A29BA-DA0D-BDD3-D9F5-A1C79953E657}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E708391A-0BA9-4A6B-8CB3-F2BE5CFE2DB1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1027,8 +1066,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12141200" y="6690919"/>
-          <a:ext cx="1885886" cy="1297382"/>
+          <a:off x="17783176" y="5789220"/>
+          <a:ext cx="1104900" cy="760108"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1040,22 +1079,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>561027</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>287655</xdr:rowOff>
+      <xdr:colOff>497527</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>81281</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1981501</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>1696236</xdr:rowOff>
+      <xdr:colOff>1714500</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>1288065</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="图片 6">
+        <xdr:cNvPr id="15" name="图片 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECE8646B-114B-ABCF-E4C9-43C831F68964}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBC229A4-3231-4AA0-8D40-4449D8075BB6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1071,8 +1110,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15884371" y="20409218"/>
-          <a:ext cx="1420474" cy="1400961"/>
+          <a:off x="18052102" y="18455006"/>
+          <a:ext cx="1216973" cy="1206784"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1084,22 +1123,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>702468</xdr:colOff>
+      <xdr:colOff>627064</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>145723</xdr:rowOff>
+      <xdr:rowOff>66349</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1762125</xdr:colOff>
+      <xdr:colOff>1476376</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>1570452</xdr:rowOff>
+      <xdr:rowOff>1208265</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="图片 7">
+        <xdr:cNvPr id="16" name="图片 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40292AB2-2B72-41A8-8175-B01F2DCAD186}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C1DA720-9051-4A2E-A54B-FF6CAEDF9B77}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1115,8 +1154,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17742693" y="13804573"/>
-          <a:ext cx="1059657" cy="1424729"/>
+          <a:off x="18181639" y="11039149"/>
+          <a:ext cx="849312" cy="1141916"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1128,22 +1167,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>488157</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>881062</xdr:rowOff>
+      <xdr:colOff>619127</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>37949</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>2559845</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>2468217</xdr:rowOff>
+      <xdr:colOff>1643063</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>1312485</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="图片 9">
+        <xdr:cNvPr id="17" name="图片 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6E4FF46-E559-4A50-9B39-EC71D473956F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB98627A-0CCB-45BE-B8F3-6A597E5DB0CC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1159,8 +1198,96 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17537907" y="16121062"/>
-          <a:ext cx="2071688" cy="1587155"/>
+          <a:off x="18180846" y="13599168"/>
+          <a:ext cx="1023936" cy="1274536"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>650875</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>101194</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1905001</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>1006602</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="图片 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6FA50C4-709F-4743-9616-4C97342E3492}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18205450" y="15074494"/>
+          <a:ext cx="1254126" cy="905408"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>599282</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>77392</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1466395</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>1222375</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="图片 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0538418-6150-4FA2-B4CF-BD9E8A1D3CB9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18153857" y="12355117"/>
+          <a:ext cx="867113" cy="1144983"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1438,74 +1565,74 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:L31"/>
+  <dimension ref="A2:L33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.625" customWidth="1"/>
     <col min="2" max="2" width="10.875" customWidth="1"/>
-    <col min="3" max="3" width="25.5" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="37.125" customWidth="1"/>
-    <col min="6" max="6" width="28.75" customWidth="1"/>
+    <col min="3" max="3" width="20.875" customWidth="1"/>
+    <col min="4" max="4" width="25.875" customWidth="1"/>
+    <col min="5" max="5" width="33.75" customWidth="1"/>
+    <col min="6" max="6" width="29.5" customWidth="1"/>
     <col min="8" max="8" width="8.875" customWidth="1"/>
-    <col min="9" max="9" width="56.875" customWidth="1"/>
+    <col min="9" max="9" width="44" customWidth="1"/>
     <col min="10" max="10" width="44.5" customWidth="1"/>
     <col min="11" max="12" width="33.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="46.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
       <c r="L2" s="15"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="39">
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="40">
         <v>46037</v>
       </c>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="38" t="s">
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="38"/>
-      <c r="J3" s="34" t="s">
+      <c r="I3" s="39"/>
+      <c r="J3" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="35"/>
+      <c r="K3" s="36"/>
     </row>
     <row r="4" spans="1:12" ht="160.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="36" t="s">
+      <c r="B4" s="27"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
       <c r="L4" s="16"/>
     </row>
     <row r="5" spans="1:12" s="1" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1544,9 +1671,9 @@
       </c>
       <c r="L5" s="17"/>
     </row>
-    <row r="6" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="4"/>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="29" t="s">
         <v>42</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -1568,7 +1695,7 @@
         <v>62</v>
       </c>
       <c r="J6" s="4"/>
-      <c r="K6" s="31" t="s">
+      <c r="K6" s="32" t="s">
         <v>57</v>
       </c>
       <c r="L6" s="12"/>
@@ -1578,7 +1705,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="29"/>
+      <c r="C7" s="30"/>
       <c r="D7" s="4" t="s">
         <v>10</v>
       </c>
@@ -1594,7 +1721,7 @@
       <c r="H7" s="4"/>
       <c r="I7" s="5"/>
       <c r="J7" s="4"/>
-      <c r="K7" s="32"/>
+      <c r="K7" s="33"/>
       <c r="L7" s="12"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -1602,7 +1729,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="4"/>
-      <c r="C8" s="29"/>
+      <c r="C8" s="30"/>
       <c r="D8" s="4" t="s">
         <v>18</v>
       </c>
@@ -1618,7 +1745,7 @@
       <c r="H8" s="4"/>
       <c r="I8" s="5"/>
       <c r="J8" s="4"/>
-      <c r="K8" s="32"/>
+      <c r="K8" s="33"/>
       <c r="L8" s="12"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -1626,7 +1753,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="29"/>
+      <c r="C9" s="30"/>
       <c r="D9" s="4" t="s">
         <v>25</v>
       </c>
@@ -1634,7 +1761,7 @@
         <v>15</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G9" s="4">
         <v>2</v>
@@ -1644,7 +1771,7 @@
         <v>60</v>
       </c>
       <c r="J9" s="4"/>
-      <c r="K9" s="32"/>
+      <c r="K9" s="33"/>
       <c r="L9" s="12"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
@@ -1652,7 +1779,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="4"/>
-      <c r="C10" s="29"/>
+      <c r="C10" s="30"/>
       <c r="D10" s="4" t="s">
         <v>23</v>
       </c>
@@ -1668,7 +1795,7 @@
       <c r="H10" s="4"/>
       <c r="I10" s="5"/>
       <c r="J10" s="4"/>
-      <c r="K10" s="32"/>
+      <c r="K10" s="33"/>
       <c r="L10" s="12"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -1676,7 +1803,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="29"/>
+      <c r="C11" s="30"/>
       <c r="D11" s="4" t="s">
         <v>19</v>
       </c>
@@ -1692,7 +1819,7 @@
       <c r="H11" s="4"/>
       <c r="I11" s="5"/>
       <c r="J11" s="4"/>
-      <c r="K11" s="32"/>
+      <c r="K11" s="33"/>
       <c r="L11" s="12"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
@@ -1700,7 +1827,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="4"/>
-      <c r="C12" s="29"/>
+      <c r="C12" s="30"/>
       <c r="D12" s="4" t="s">
         <v>20</v>
       </c>
@@ -1716,7 +1843,7 @@
       <c r="H12" s="4"/>
       <c r="I12" s="5"/>
       <c r="J12" s="4"/>
-      <c r="K12" s="32"/>
+      <c r="K12" s="33"/>
       <c r="L12" s="12"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -1724,7 +1851,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="4"/>
-      <c r="C13" s="29"/>
+      <c r="C13" s="30"/>
       <c r="D13" s="4" t="s">
         <v>22</v>
       </c>
@@ -1740,7 +1867,7 @@
       <c r="H13" s="4"/>
       <c r="I13" s="5"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="32"/>
+      <c r="K13" s="33"/>
       <c r="L13" s="12"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
@@ -1748,7 +1875,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="4"/>
-      <c r="C14" s="29"/>
+      <c r="C14" s="30"/>
       <c r="D14" s="4" t="s">
         <v>24</v>
       </c>
@@ -1764,7 +1891,7 @@
       <c r="H14" s="4"/>
       <c r="I14" s="5"/>
       <c r="J14" s="4"/>
-      <c r="K14" s="32"/>
+      <c r="K14" s="33"/>
       <c r="L14" s="12"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -1772,7 +1899,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="4"/>
-      <c r="C15" s="29"/>
+      <c r="C15" s="30"/>
       <c r="D15" s="4" t="s">
         <v>27</v>
       </c>
@@ -1788,7 +1915,7 @@
       <c r="H15" s="4"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
-      <c r="K15" s="32"/>
+      <c r="K15" s="33"/>
       <c r="L15" s="12"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
@@ -1796,7 +1923,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="4"/>
-      <c r="C16" s="29"/>
+      <c r="C16" s="30"/>
       <c r="D16" s="4" t="s">
         <v>28</v>
       </c>
@@ -1812,7 +1939,7 @@
       <c r="H16" s="4"/>
       <c r="I16" s="5"/>
       <c r="J16" s="4"/>
-      <c r="K16" s="32"/>
+      <c r="K16" s="33"/>
       <c r="L16" s="12"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
@@ -1820,7 +1947,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="4"/>
-      <c r="C17" s="29"/>
+      <c r="C17" s="30"/>
       <c r="D17" s="4" t="s">
         <v>33</v>
       </c>
@@ -1840,15 +1967,15 @@
         <v>68</v>
       </c>
       <c r="J17" s="4"/>
-      <c r="K17" s="32"/>
+      <c r="K17" s="33"/>
       <c r="L17" s="12"/>
     </row>
-    <row r="18" spans="1:12" ht="130.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>12</v>
       </c>
       <c r="B18" s="4"/>
-      <c r="C18" s="29"/>
+      <c r="C18" s="30"/>
       <c r="D18" s="4" t="s">
         <v>35</v>
       </c>
@@ -1864,15 +1991,15 @@
       </c>
       <c r="I18" s="5"/>
       <c r="J18" s="4"/>
-      <c r="K18" s="32"/>
+      <c r="K18" s="33"/>
       <c r="L18" s="12"/>
     </row>
-    <row r="19" spans="1:12" ht="123.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>13</v>
       </c>
       <c r="B19" s="4"/>
-      <c r="C19" s="29"/>
+      <c r="C19" s="30"/>
       <c r="D19" s="4" t="s">
         <v>37</v>
       </c>
@@ -1888,15 +2015,15 @@
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="4"/>
-      <c r="K19" s="32"/>
+      <c r="K19" s="33"/>
       <c r="L19" s="12"/>
     </row>
-    <row r="20" spans="1:12" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>14</v>
       </c>
       <c r="B20" s="4"/>
-      <c r="C20" s="29"/>
+      <c r="C20" s="30"/>
       <c r="D20" s="4" t="s">
         <v>38</v>
       </c>
@@ -1912,15 +2039,15 @@
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="4"/>
-      <c r="K20" s="32"/>
+      <c r="K20" s="33"/>
       <c r="L20" s="12"/>
     </row>
-    <row r="21" spans="1:12" ht="121.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>15</v>
       </c>
       <c r="B21" s="4"/>
-      <c r="C21" s="29"/>
+      <c r="C21" s="30"/>
       <c r="D21" s="4" t="s">
         <v>39</v>
       </c>
@@ -1936,15 +2063,15 @@
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="4"/>
-      <c r="K21" s="32"/>
+      <c r="K21" s="33"/>
       <c r="L21" s="12"/>
     </row>
-    <row r="22" spans="1:12" ht="127.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="93.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>16</v>
       </c>
       <c r="B22" s="4"/>
-      <c r="C22" s="30"/>
+      <c r="C22" s="31"/>
       <c r="D22" s="4" t="s">
         <v>40</v>
       </c>
@@ -1960,38 +2087,42 @@
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="4"/>
-      <c r="K22" s="32"/>
+      <c r="K22" s="33"/>
       <c r="L22" s="12"/>
     </row>
-    <row r="23" spans="1:12" ht="127.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="102.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>17</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>43</v>
       </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
+      <c r="G23" s="4">
+        <v>1</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="I23" s="5"/>
       <c r="J23" s="4"/>
-      <c r="K23" s="40" t="s">
-        <v>81</v>
+      <c r="K23" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="L23" s="12"/>
     </row>
-    <row r="24" spans="1:12" ht="251.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="103.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>18</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>43</v>
@@ -2007,188 +2138,247 @@
       <c r="I24" s="8"/>
       <c r="J24" s="4"/>
       <c r="K24" s="9" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="L24" s="12"/>
     </row>
-    <row r="25" spans="1:12" ht="82.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="108.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>19</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>43</v>
       </c>
       <c r="E25" s="4"/>
-      <c r="F25" s="4" t="s">
-        <v>75</v>
-      </c>
+      <c r="F25" s="4"/>
       <c r="G25" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="I25" s="20" t="s">
-        <v>77</v>
+      <c r="I25" s="41" t="s">
+        <v>84</v>
       </c>
       <c r="J25" s="4"/>
       <c r="K25" s="9" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L25" s="12"/>
     </row>
-    <row r="26" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="87" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>20</v>
       </c>
-      <c r="B26" s="7"/>
+      <c r="B26" s="4"/>
       <c r="C26" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>72</v>
+        <v>86</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="G26" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I26" s="5"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="L26" s="18"/>
-    </row>
-    <row r="27" spans="1:12" ht="156" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I26" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="J26" s="4"/>
+      <c r="K26" s="42" t="s">
+        <v>88</v>
+      </c>
+      <c r="L26" s="12"/>
+    </row>
+    <row r="27" spans="1:12" ht="82.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>21</v>
       </c>
-      <c r="B27" s="7"/>
+      <c r="B27" s="4"/>
       <c r="C27" s="4" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
+      <c r="F27" s="4" t="s">
+        <v>74</v>
+      </c>
       <c r="G27" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="J27" s="7"/>
-      <c r="K27" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="L27" s="18"/>
-    </row>
-    <row r="28" spans="1:12" ht="147.6" customHeight="1" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+      <c r="I27" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="J27" s="4"/>
+      <c r="K27" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L27" s="12"/>
+    </row>
+    <row r="28" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>22</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>71</v>
+      </c>
       <c r="G28" s="4">
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J28" s="4"/>
-      <c r="K28" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="L28" s="12"/>
-    </row>
-    <row r="29" spans="1:12" ht="107.45" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+      <c r="I28" s="5"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="L28" s="18"/>
+    </row>
+    <row r="29" spans="1:12" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>23</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="4" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>46</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
       <c r="G29" s="4">
         <v>1</v>
       </c>
       <c r="H29" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J29" s="7"/>
+      <c r="K29" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="L29" s="18"/>
+    </row>
+    <row r="30" spans="1:12" ht="147.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="4">
+        <v>24</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4">
+        <v>1</v>
+      </c>
+      <c r="H30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="I29" s="10" t="s">
+      <c r="I30" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J30" s="4"/>
+      <c r="K30" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="L30" s="12"/>
+    </row>
+    <row r="31" spans="1:12" ht="107.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="4">
+        <v>25</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G31" s="4">
+        <v>1</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I31" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J29" s="7"/>
-      <c r="L29" s="18"/>
-    </row>
-    <row r="30" spans="1:12" ht="55.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
+      <c r="J31" s="7"/>
+      <c r="K31" s="43"/>
+      <c r="L31" s="18"/>
+    </row>
+    <row r="32" spans="1:12" ht="55.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
-      <c r="J30" s="24"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="14"/>
-    </row>
-    <row r="31" spans="1:12" ht="55.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="12"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
+      <c r="B32" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="14"/>
+    </row>
+    <row r="33" spans="1:12" ht="55.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="12"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B30:K30"/>
+    <mergeCell ref="B32:K32"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="C6:C22"/>
     <mergeCell ref="K6:K22"/>
@@ -2201,10 +2391,11 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="K27" r:id="rId1" display="https://item.taobao.com/item.htm?abbucket=19&amp;id=885032361201&amp;mi_id=0000jfJCKwilSELr-zj6p1uyrAQwxlg-lD2tJdTGwlUgR0Q&amp;ns=1&amp;priceTId=214784af17684674532951853e134d&amp;skuId=5893464791989&amp;spm=a21n57.1.hoverItem.2&amp;utparam=%7B%22aplus_abtest%22%3A%2225b53b868684608ed1ab462bacf635cd%22%7D&amp;xxc=taobaoSearch" xr:uid="{8F128C67-311B-47D8-AE93-CC2347C1CC97}"/>
+    <hyperlink ref="K29" r:id="rId1" display="https://item.taobao.com/item.htm?abbucket=19&amp;id=885032361201&amp;mi_id=0000jfJCKwilSELr-zj6p1uyrAQwxlg-lD2tJdTGwlUgR0Q&amp;ns=1&amp;priceTId=214784af17684674532951853e134d&amp;skuId=5893464791989&amp;spm=a21n57.1.hoverItem.2&amp;utparam=%7B%22aplus_abtest%22%3A%2225b53b868684608ed1ab462bacf635cd%22%7D&amp;xxc=taobaoSearch" xr:uid="{3015715C-E3FC-4EC8-9968-9E56D711F6C4}"/>
+    <hyperlink ref="K26" r:id="rId2" xr:uid="{B260531E-FF71-471F-9440-088756E7A4C7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.44" top="0.25" bottom="0.16" header="0.12" footer="0.09"/>
-  <pageSetup paperSize="9" scale="29" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup paperSize="9" scale="31" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>